--- a/public/templates/SEÑAS_Excel_Student_Import.xlsx
+++ b/public/templates/SEÑAS_Excel_Student_Import.xlsx
@@ -114,7 +114,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>lrn</t>
   </si>
@@ -138,6 +138,18 @@
   </si>
   <si>
     <t>section</t>
+  </si>
+  <si>
+    <t>mother_name</t>
+  </si>
+  <si>
+    <t>father_name</t>
+  </si>
+  <si>
+    <t>emergency_contact_name</t>
+  </si>
+  <si>
+    <t>emergency_contact_number</t>
   </si>
 </sst>
 </file>
@@ -199,11 +211,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -506,7 +519,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:L1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -514,10 +527,13 @@
     <col min="4" max="4" width="10" customWidth="1"/>
     <col min="5" max="5" width="18" customWidth="1"/>
     <col min="6" max="6" width="20" customWidth="1"/>
-    <col min="7" max="9" width="15" customWidth="1"/>
+    <col min="7" max="8" width="15" customWidth="1"/>
+    <col min="9" max="10" width="22" customWidth="1"/>
+    <col min="11" max="11" width="30" customWidth="1"/>
+    <col min="12" max="12" width="30" customWidth="1" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -541,6 +557,18 @@
       </c>
       <c r="H1" s="1" t="s">
         <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
